--- a/backend/import_formations_reel.xlsx
+++ b/backend/import_formations_reel.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K184"/>
+  <dimension ref="A1:M184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -501,35 +501,45 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Bâtiment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Salle</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Date début</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Date fin</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Volume horaire (h)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Groupe</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Vague</t>
         </is>
@@ -554,31 +564,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="6" t="n">
         <v>46129.33333333334</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="H2" s="6" t="n">
         <v>46130.70833333334</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>16</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -603,31 +615,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" s="6" t="n">
         <v>46154.33333333334</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>46158.70833333334</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>30</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -652,31 +666,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="H4" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>30</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -701,31 +717,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
         <v>46172.33333333334</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>46173.70833333334</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>16</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -750,31 +768,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="H6" s="6" t="n">
         <v>46153.70833333334</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>30</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -799,31 +819,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="H7" s="6" t="n">
         <v>46171.70833333334</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>16</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -848,31 +870,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="H8" s="6" t="n">
         <v>46132.70833333334</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>16</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -897,31 +921,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="H9" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>30</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -946,31 +972,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="H10" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>20</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -995,31 +1023,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" s="6" t="n">
         <v>46137.33333333334</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>46138.70833333334</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>16</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1044,31 +1074,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="H12" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>30</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1093,31 +1125,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" s="6" t="n">
         <v>46157.33333333334</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="H13" s="6" t="n">
         <v>46161.70833333334</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>30</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1142,31 +1176,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="H14" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>16</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1191,31 +1227,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="H15" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>30</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1240,31 +1278,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="H16" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>16</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1289,31 +1329,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" s="6" t="n">
         <v>46139.33333333334</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="H17" s="6" t="n">
         <v>46140.70833333334</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>16</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1338,31 +1380,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" s="6" t="n">
         <v>46162.33333333334</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="H18" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>30</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1387,31 +1431,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="H19" s="6" t="n">
         <v>46155.70833333334</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>20</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>GROUPE 10</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1436,31 +1482,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
         <v>46129.33333333334</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="H20" s="6" t="n">
         <v>46130.70833333334</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>16</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1485,31 +1533,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
         <v>46154.33333333334</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="H21" s="6" t="n">
         <v>46158.70833333334</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>30</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1534,31 +1584,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="H22" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>30</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1583,31 +1635,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" s="6" t="n">
         <v>46172.33333333334</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="H23" s="6" t="n">
         <v>46173.70833333334</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>16</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1632,31 +1686,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="H24" s="6" t="n">
         <v>46153.70833333334</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>30</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1681,31 +1737,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="H25" s="6" t="n">
         <v>46171.70833333334</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>16</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1730,31 +1788,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="H26" s="6" t="n">
         <v>46132.70833333334</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>16</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1779,31 +1839,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="H27" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>30</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1828,31 +1890,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="H28" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G28" t="n">
+      <c r="I28" t="n">
         <v>20</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1877,31 +1941,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" s="6" t="n">
         <v>46129.33333333334</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="H29" s="6" t="n">
         <v>46130.70833333334</v>
       </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
         <v>16</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1926,31 +1992,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" s="6" t="n">
         <v>46154.33333333334</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="H30" s="6" t="n">
         <v>46158.70833333334</v>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>30</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1975,31 +2043,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="H31" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G31" t="n">
+      <c r="I31" t="n">
         <v>30</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2024,31 +2094,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" s="6" t="n">
         <v>46172.33333333334</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="H32" s="6" t="n">
         <v>46173.70833333334</v>
       </c>
-      <c r="G32" t="n">
+      <c r="I32" t="n">
         <v>16</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2073,31 +2145,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="H33" s="6" t="n">
         <v>46153.70833333334</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>30</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2122,31 +2196,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="H34" s="6" t="n">
         <v>46171.70833333334</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>16</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2171,31 +2247,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" s="6" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="H35" s="6" t="n">
         <v>46132.70833333334</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>16</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2220,31 +2298,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="H36" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
         <v>30</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2269,31 +2349,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="H37" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>20</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2318,31 +2400,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" s="6" t="n">
         <v>46133.33333333334</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="H38" s="6" t="n">
         <v>46134.70833333334</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>16</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2367,31 +2451,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" s="6" t="n">
         <v>46154.33333333334</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="H39" s="6" t="n">
         <v>46158.70833333334</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>30</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2416,31 +2502,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="H40" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>30</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2465,31 +2553,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" s="6" t="n">
         <v>46172.33333333334</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="H41" s="6" t="n">
         <v>46173.70833333334</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>16</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2514,31 +2604,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="H42" s="6" t="n">
         <v>46153.70833333334</v>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>30</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2563,31 +2655,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="H43" s="6" t="n">
         <v>46171.70833333334</v>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>16</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2612,31 +2706,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" s="6" t="n">
         <v>46135.33333333334</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="H44" s="6" t="n">
         <v>46136.70833333334</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I44" t="n">
         <v>16</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2661,31 +2757,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="H45" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G45" t="n">
+      <c r="I45" t="n">
         <v>30</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2710,31 +2808,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="H46" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>20</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2759,31 +2859,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" s="6" t="n">
         <v>46133.33333333334</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="H47" s="6" t="n">
         <v>46134.70833333334</v>
       </c>
-      <c r="G47" t="n">
+      <c r="I47" t="n">
         <v>16</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2808,31 +2910,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" s="6" t="n">
         <v>46154.33333333334</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="H48" s="6" t="n">
         <v>46158.70833333334</v>
       </c>
-      <c r="G48" t="n">
+      <c r="I48" t="n">
         <v>30</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2857,31 +2961,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="H49" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G49" t="n">
+      <c r="I49" t="n">
         <v>30</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2906,31 +3012,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" s="6" t="n">
         <v>46172.33333333334</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="H50" s="6" t="n">
         <v>46173.70833333334</v>
       </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
         <v>16</v>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -2955,31 +3063,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="H51" s="6" t="n">
         <v>46153.70833333334</v>
       </c>
-      <c r="G51" t="n">
+      <c r="I51" t="n">
         <v>30</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3004,31 +3114,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="H52" s="6" t="n">
         <v>46171.70833333334</v>
       </c>
-      <c r="G52" t="n">
+      <c r="I52" t="n">
         <v>16</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3053,31 +3165,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" s="6" t="n">
         <v>46135.33333333334</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="H53" s="6" t="n">
         <v>46136.70833333334</v>
       </c>
-      <c r="G53" t="n">
+      <c r="I53" t="n">
         <v>16</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3102,31 +3216,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="H54" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
         <v>30</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3151,31 +3267,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="H55" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
         <v>20</v>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3200,31 +3318,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" s="6" t="n">
         <v>46133.33333333334</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="H56" s="6" t="n">
         <v>46134.70833333334</v>
       </c>
-      <c r="G56" t="n">
+      <c r="I56" t="n">
         <v>16</v>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3249,31 +3369,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="H57" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G57" t="n">
+      <c r="I57" t="n">
         <v>30</v>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3298,31 +3420,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" s="6" t="n">
         <v>46157.33333333334</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="H58" s="6" t="n">
         <v>46161.70833333334</v>
       </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
         <v>30</v>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3347,31 +3471,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="H59" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G59" t="n">
+      <c r="I59" t="n">
         <v>16</v>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3396,31 +3522,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="H60" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
         <v>30</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3445,31 +3573,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="H61" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G61" t="n">
+      <c r="I61" t="n">
         <v>16</v>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3494,31 +3624,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" s="6" t="n">
         <v>46135.33333333334</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="H62" s="6" t="n">
         <v>46136.70833333334</v>
       </c>
-      <c r="G62" t="n">
+      <c r="I62" t="n">
         <v>16</v>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3543,31 +3675,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" s="6" t="n">
         <v>46162.33333333334</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="H63" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G63" t="n">
+      <c r="I63" t="n">
         <v>30</v>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3592,31 +3726,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="H64" s="6" t="n">
         <v>46155.70833333334</v>
       </c>
-      <c r="G64" t="n">
+      <c r="I64" t="n">
         <v>20</v>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3641,31 +3777,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" s="6" t="n">
         <v>46133.33333333334</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="H65" s="6" t="n">
         <v>46134.70833333334</v>
       </c>
-      <c r="G65" t="n">
+      <c r="I65" t="n">
         <v>16</v>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3690,31 +3828,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="H66" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G66" t="n">
+      <c r="I66" t="n">
         <v>30</v>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3739,31 +3879,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" s="6" t="n">
         <v>46157.33333333334</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="H67" s="6" t="n">
         <v>46161.70833333334</v>
       </c>
-      <c r="G67" t="n">
+      <c r="I67" t="n">
         <v>30</v>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3788,31 +3930,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="H68" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G68" t="n">
+      <c r="I68" t="n">
         <v>16</v>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3837,31 +3981,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="H69" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G69" t="n">
+      <c r="I69" t="n">
         <v>30</v>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3886,31 +4032,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="H70" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G70" t="n">
+      <c r="I70" t="n">
         <v>16</v>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3935,31 +4083,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" s="6" t="n">
         <v>46135.33333333334</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="H71" s="6" t="n">
         <v>46136.70833333334</v>
       </c>
-      <c r="G71" t="n">
+      <c r="I71" t="n">
         <v>16</v>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3984,31 +4134,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" s="6" t="n">
         <v>46162.33333333334</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="H72" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G72" t="n">
+      <c r="I72" t="n">
         <v>30</v>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4033,31 +4185,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="H73" s="6" t="n">
         <v>46155.70833333334</v>
       </c>
-      <c r="G73" t="n">
+      <c r="I73" t="n">
         <v>20</v>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4082,31 +4236,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" s="6" t="n">
         <v>46133.33333333334</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="H74" s="6" t="n">
         <v>46134.70833333334</v>
       </c>
-      <c r="G74" t="n">
+      <c r="I74" t="n">
         <v>16</v>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4131,31 +4287,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="H75" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
         <v>30</v>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4180,31 +4338,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" s="6" t="n">
         <v>46157.33333333334</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="H76" s="6" t="n">
         <v>46161.70833333334</v>
       </c>
-      <c r="G76" t="n">
+      <c r="I76" t="n">
         <v>30</v>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4229,31 +4389,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="H77" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G77" t="n">
+      <c r="I77" t="n">
         <v>16</v>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4278,31 +4440,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="H78" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G78" t="n">
+      <c r="I78" t="n">
         <v>30</v>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4327,31 +4491,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="H79" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G79" t="n">
+      <c r="I79" t="n">
         <v>16</v>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4376,31 +4542,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" s="6" t="n">
         <v>46135.33333333334</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="H80" s="6" t="n">
         <v>46136.70833333334</v>
       </c>
-      <c r="G80" t="n">
+      <c r="I80" t="n">
         <v>16</v>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4425,31 +4593,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" s="6" t="n">
         <v>46162.33333333334</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="H81" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G81" t="n">
+      <c r="I81" t="n">
         <v>30</v>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4474,31 +4644,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="H82" s="6" t="n">
         <v>46155.70833333334</v>
       </c>
-      <c r="G82" t="n">
+      <c r="I82" t="n">
         <v>20</v>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4523,31 +4695,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" s="6" t="n">
         <v>46137.33333333334</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="H83" s="6" t="n">
         <v>46138.70833333334</v>
       </c>
-      <c r="G83" t="n">
+      <c r="I83" t="n">
         <v>16</v>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4572,31 +4746,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="H84" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G84" t="n">
+      <c r="I84" t="n">
         <v>30</v>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4621,31 +4797,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" s="6" t="n">
         <v>46157.33333333334</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="H85" s="6" t="n">
         <v>46161.70833333334</v>
       </c>
-      <c r="G85" t="n">
+      <c r="I85" t="n">
         <v>30</v>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4670,31 +4848,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="H86" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G86" t="n">
+      <c r="I86" t="n">
         <v>16</v>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4719,31 +4899,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E87" s="6" t="n">
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F87" s="6" t="n">
+      <c r="H87" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G87" t="n">
+      <c r="I87" t="n">
         <v>30</v>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4768,31 +4950,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E88" s="6" t="n">
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F88" s="6" t="n">
+      <c r="H88" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G88" t="n">
+      <c r="I88" t="n">
         <v>16</v>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4817,31 +5001,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E89" s="6" t="n">
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" s="6" t="n">
         <v>46139.33333333334</v>
       </c>
-      <c r="F89" s="6" t="n">
+      <c r="H89" s="6" t="n">
         <v>46140.70833333334</v>
       </c>
-      <c r="G89" t="n">
+      <c r="I89" t="n">
         <v>16</v>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4866,31 +5052,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" s="6" t="n">
         <v>46162.33333333334</v>
       </c>
-      <c r="F90" s="6" t="n">
+      <c r="H90" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G90" t="n">
+      <c r="I90" t="n">
         <v>30</v>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4915,31 +5103,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="H91" s="6" t="n">
         <v>46155.70833333334</v>
       </c>
-      <c r="G91" t="n">
+      <c r="I91" t="n">
         <v>20</v>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>GROUPE 9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -4964,31 +5154,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" s="6" t="n">
         <v>46125.33333333334</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="H92" s="6" t="n">
         <v>46126.70833333334</v>
       </c>
-      <c r="G92" t="n">
+      <c r="I92" t="n">
         <v>16</v>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5013,31 +5205,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" s="6" t="n">
         <v>46158.33333333334</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G93" t="n">
+      <c r="I93" t="n">
         <v>30</v>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5062,31 +5256,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>46157.70833333334</v>
       </c>
-      <c r="G94" t="n">
+      <c r="I94" t="n">
         <v>30</v>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5111,31 +5307,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E95" s="6" t="n">
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F95" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G95" t="n">
+      <c r="I95" t="n">
         <v>16</v>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5160,31 +5358,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" s="6" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="H96" s="6" t="n">
         <v>46180.70833333334</v>
       </c>
-      <c r="G96" t="n">
+      <c r="I96" t="n">
         <v>30</v>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5209,31 +5409,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E97" s="6" t="n">
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="H97" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G97" t="n">
+      <c r="I97" t="n">
         <v>16</v>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5258,31 +5460,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E98" s="6" t="n">
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F98" s="6" t="n">
+      <c r="H98" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G98" t="n">
+      <c r="I98" t="n">
         <v>30</v>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5307,31 +5511,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n">
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" s="6" t="n">
         <v>46127.33333333334</v>
       </c>
-      <c r="F99" s="6" t="n">
+      <c r="H99" s="6" t="n">
         <v>46128.70833333334</v>
       </c>
-      <c r="G99" t="n">
+      <c r="I99" t="n">
         <v>16</v>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5356,31 +5562,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n">
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F100" s="6" t="n">
+      <c r="H100" s="6" t="n">
         <v>46175.70833333334</v>
       </c>
-      <c r="G100" t="n">
+      <c r="I100" t="n">
         <v>30</v>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5405,31 +5613,33 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E101" s="6" t="n">
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="H101" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G101" t="n">
+      <c r="I101" t="n">
         <v>20</v>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5454,31 +5664,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" s="6" t="n">
         <v>46125.33333333334</v>
       </c>
-      <c r="F102" s="6" t="n">
+      <c r="H102" s="6" t="n">
         <v>46126.70833333334</v>
       </c>
-      <c r="G102" t="n">
+      <c r="I102" t="n">
         <v>16</v>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5503,31 +5715,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E103" s="6" t="n">
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" s="6" t="n">
         <v>46158.33333333334</v>
       </c>
-      <c r="F103" s="6" t="n">
+      <c r="H103" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G103" t="n">
+      <c r="I103" t="n">
         <v>30</v>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5552,31 +5766,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E104" s="6" t="n">
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F104" s="6" t="n">
+      <c r="H104" s="6" t="n">
         <v>46157.70833333334</v>
       </c>
-      <c r="G104" t="n">
+      <c r="I104" t="n">
         <v>30</v>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5601,31 +5817,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E105" s="6" t="n">
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F105" s="6" t="n">
+      <c r="H105" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G105" t="n">
+      <c r="I105" t="n">
         <v>16</v>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5650,31 +5868,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E106" s="6" t="n">
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" s="6" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F106" s="6" t="n">
+      <c r="H106" s="6" t="n">
         <v>46180.70833333334</v>
       </c>
-      <c r="G106" t="n">
+      <c r="I106" t="n">
         <v>30</v>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5699,31 +5919,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E107" s="6" t="n">
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F107" s="6" t="n">
+      <c r="H107" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G107" t="n">
+      <c r="I107" t="n">
         <v>16</v>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5748,31 +5970,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E108" s="6" t="n">
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F108" s="6" t="n">
+      <c r="H108" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G108" t="n">
+      <c r="I108" t="n">
         <v>30</v>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5797,31 +6021,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" s="6" t="n">
         <v>46127.33333333334</v>
       </c>
-      <c r="F109" s="6" t="n">
+      <c r="H109" s="6" t="n">
         <v>46128.70833333334</v>
       </c>
-      <c r="G109" t="n">
+      <c r="I109" t="n">
         <v>16</v>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5846,31 +6072,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E110" s="6" t="n">
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F110" s="6" t="n">
+      <c r="H110" s="6" t="n">
         <v>46175.70833333334</v>
       </c>
-      <c r="G110" t="n">
+      <c r="I110" t="n">
         <v>30</v>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5895,31 +6123,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E111" s="6" t="n">
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F111" s="6" t="n">
+      <c r="H111" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G111" t="n">
+      <c r="I111" t="n">
         <v>20</v>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5944,31 +6174,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E112" s="6" t="n">
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" s="6" t="n">
         <v>46125.33333333334</v>
       </c>
-      <c r="F112" s="6" t="n">
+      <c r="H112" s="6" t="n">
         <v>46126.70833333334</v>
       </c>
-      <c r="G112" t="n">
+      <c r="I112" t="n">
         <v>16</v>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -5993,31 +6225,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E113" s="6" t="n">
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" s="6" t="n">
         <v>46158.33333333334</v>
       </c>
-      <c r="F113" s="6" t="n">
+      <c r="H113" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G113" t="n">
+      <c r="I113" t="n">
         <v>30</v>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6042,31 +6276,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E114" s="6" t="n">
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F114" s="6" t="n">
+      <c r="H114" s="6" t="n">
         <v>46157.70833333334</v>
       </c>
-      <c r="G114" t="n">
+      <c r="I114" t="n">
         <v>30</v>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6091,31 +6327,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E115" s="6" t="n">
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" s="6" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F115" s="6" t="n">
+      <c r="H115" s="6" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G115" t="n">
+      <c r="I115" t="n">
         <v>16</v>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6140,31 +6378,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E116" s="6" t="n">
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" s="6" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F116" s="6" t="n">
+      <c r="H116" s="6" t="n">
         <v>46180.70833333334</v>
       </c>
-      <c r="G116" t="n">
+      <c r="I116" t="n">
         <v>30</v>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6189,31 +6429,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E117" s="6" t="n">
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F117" s="6" t="n">
+      <c r="H117" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G117" t="n">
+      <c r="I117" t="n">
         <v>16</v>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6238,31 +6480,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E118" s="6" t="n">
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F118" s="6" t="n">
+      <c r="H118" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G118" t="n">
+      <c r="I118" t="n">
         <v>30</v>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6287,31 +6531,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E119" s="6" t="n">
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" s="6" t="n">
         <v>46127.33333333334</v>
       </c>
-      <c r="F119" s="6" t="n">
+      <c r="H119" s="6" t="n">
         <v>46128.70833333334</v>
       </c>
-      <c r="G119" t="n">
+      <c r="I119" t="n">
         <v>16</v>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6336,31 +6582,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E120" s="6" t="n">
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" s="6" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F120" s="6" t="n">
+      <c r="H120" s="6" t="n">
         <v>46175.70833333334</v>
       </c>
-      <c r="G120" t="n">
+      <c r="I120" t="n">
         <v>30</v>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6385,31 +6633,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E121" s="6" t="n">
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F121" s="6" t="n">
+      <c r="H121" s="6" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G121" t="n">
+      <c r="I121" t="n">
         <v>20</v>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6434,31 +6684,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E122" s="6" t="n">
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" s="6" t="n">
         <v>46125.33333333334</v>
       </c>
-      <c r="F122" s="6" t="n">
+      <c r="H122" s="6" t="n">
         <v>46126.70833333334</v>
       </c>
-      <c r="G122" t="n">
+      <c r="I122" t="n">
         <v>16</v>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6483,31 +6735,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E123" s="6" t="n">
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F123" s="6" t="n">
+      <c r="H123" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G123" t="n">
+      <c r="I123" t="n">
         <v>30</v>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6532,31 +6786,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E124" s="6" t="n">
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F124" s="6" t="n">
+      <c r="H124" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G124" t="n">
+      <c r="I124" t="n">
         <v>30</v>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6581,31 +6837,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E125" s="6" t="n">
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" s="6" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F125" s="6" t="n">
+      <c r="H125" s="6" t="n">
         <v>46178.70833333334</v>
       </c>
-      <c r="G125" t="n">
+      <c r="I125" t="n">
         <v>16</v>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6630,31 +6888,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E126" s="6" t="n">
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" s="6" t="n">
         <v>46155.33333333334</v>
       </c>
-      <c r="F126" s="6" t="n">
+      <c r="H126" s="6" t="n">
         <v>46159.70833333334</v>
       </c>
-      <c r="G126" t="n">
+      <c r="I126" t="n">
         <v>30</v>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6679,31 +6939,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E127" s="6" t="n">
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" s="6" t="n">
         <v>46175.33333333334</v>
       </c>
-      <c r="F127" s="6" t="n">
+      <c r="H127" s="6" t="n">
         <v>46176.70833333334</v>
       </c>
-      <c r="G127" t="n">
+      <c r="I127" t="n">
         <v>16</v>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6728,31 +6990,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E128" s="6" t="n">
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F128" s="6" t="n">
+      <c r="H128" s="6" t="n">
         <v>46154.70833333334</v>
       </c>
-      <c r="G128" t="n">
+      <c r="I128" t="n">
         <v>30</v>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6777,31 +7041,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E129" s="6" t="n">
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" s="6" t="n">
         <v>46127.33333333334</v>
       </c>
-      <c r="F129" s="6" t="n">
+      <c r="H129" s="6" t="n">
         <v>46128.70833333334</v>
       </c>
-      <c r="G129" t="n">
+      <c r="I129" t="n">
         <v>16</v>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6826,31 +7092,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E130" s="6" t="n">
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F130" s="6" t="n">
+      <c r="H130" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G130" t="n">
+      <c r="I130" t="n">
         <v>30</v>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6875,31 +7143,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E131" s="6" t="n">
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F131" s="6" t="n">
+      <c r="H131" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G131" t="n">
+      <c r="I131" t="n">
         <v>20</v>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t>GROUPE 4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6924,31 +7194,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E132" s="6" t="n">
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" s="6" t="n">
         <v>46125.33333333334</v>
       </c>
-      <c r="F132" s="6" t="n">
+      <c r="H132" s="6" t="n">
         <v>46126.70833333334</v>
       </c>
-      <c r="G132" t="n">
+      <c r="I132" t="n">
         <v>16</v>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -6973,31 +7245,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E133" s="6" t="n">
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F133" s="6" t="n">
+      <c r="H133" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G133" t="n">
+      <c r="I133" t="n">
         <v>30</v>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7022,31 +7296,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E134" s="6" t="n">
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F134" s="6" t="n">
+      <c r="H134" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G134" t="n">
+      <c r="I134" t="n">
         <v>30</v>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7071,31 +7347,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E135" s="6" t="n">
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" s="6" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F135" s="6" t="n">
+      <c r="H135" s="6" t="n">
         <v>46178.70833333334</v>
       </c>
-      <c r="G135" t="n">
+      <c r="I135" t="n">
         <v>16</v>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7120,31 +7398,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E136" s="6" t="n">
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" s="6" t="n">
         <v>46155.33333333334</v>
       </c>
-      <c r="F136" s="6" t="n">
+      <c r="H136" s="6" t="n">
         <v>46159.70833333334</v>
       </c>
-      <c r="G136" t="n">
+      <c r="I136" t="n">
         <v>30</v>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7169,31 +7449,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E137" s="6" t="n">
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" s="6" t="n">
         <v>46175.33333333334</v>
       </c>
-      <c r="F137" s="6" t="n">
+      <c r="H137" s="6" t="n">
         <v>46176.70833333334</v>
       </c>
-      <c r="G137" t="n">
+      <c r="I137" t="n">
         <v>16</v>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7218,31 +7500,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E138" s="6" t="n">
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F138" s="6" t="n">
+      <c r="H138" s="6" t="n">
         <v>46154.70833333334</v>
       </c>
-      <c r="G138" t="n">
+      <c r="I138" t="n">
         <v>30</v>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7267,31 +7551,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E139" s="6" t="n">
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" s="6" t="n">
         <v>46127.33333333334</v>
       </c>
-      <c r="F139" s="6" t="n">
+      <c r="H139" s="6" t="n">
         <v>46128.70833333334</v>
       </c>
-      <c r="G139" t="n">
+      <c r="I139" t="n">
         <v>16</v>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7316,31 +7602,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E140" s="6" t="n">
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F140" s="6" t="n">
+      <c r="H140" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G140" t="n">
+      <c r="I140" t="n">
         <v>30</v>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7365,31 +7653,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E141" s="6" t="n">
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F141" s="6" t="n">
+      <c r="H141" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G141" t="n">
+      <c r="I141" t="n">
         <v>20</v>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t>GROUPE 5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7414,31 +7704,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E142" s="6" t="n">
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" s="6" t="n">
         <v>46129.33333333334</v>
       </c>
-      <c r="F142" s="6" t="n">
+      <c r="H142" s="6" t="n">
         <v>46130.70833333334</v>
       </c>
-      <c r="G142" t="n">
+      <c r="I142" t="n">
         <v>16</v>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7463,31 +7755,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E143" s="6" t="n">
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F143" s="6" t="n">
+      <c r="H143" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G143" t="n">
+      <c r="I143" t="n">
         <v>30</v>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7512,31 +7806,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E144" s="6" t="n">
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F144" s="6" t="n">
+      <c r="H144" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G144" t="n">
+      <c r="I144" t="n">
         <v>30</v>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7561,31 +7857,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E145" s="6" t="n">
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" s="6" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F145" s="6" t="n">
+      <c r="H145" s="6" t="n">
         <v>46178.70833333334</v>
       </c>
-      <c r="G145" t="n">
+      <c r="I145" t="n">
         <v>16</v>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7610,31 +7908,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E146" s="6" t="n">
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" s="6" t="n">
         <v>46155.33333333334</v>
       </c>
-      <c r="F146" s="6" t="n">
+      <c r="H146" s="6" t="n">
         <v>46159.70833333334</v>
       </c>
-      <c r="G146" t="n">
+      <c r="I146" t="n">
         <v>30</v>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7659,31 +7959,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E147" s="6" t="n">
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" s="6" t="n">
         <v>46175.33333333334</v>
       </c>
-      <c r="F147" s="6" t="n">
+      <c r="H147" s="6" t="n">
         <v>46176.70833333334</v>
       </c>
-      <c r="G147" t="n">
+      <c r="I147" t="n">
         <v>16</v>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7708,31 +8010,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E148" s="6" t="n">
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F148" s="6" t="n">
+      <c r="H148" s="6" t="n">
         <v>46154.70833333334</v>
       </c>
-      <c r="G148" t="n">
+      <c r="I148" t="n">
         <v>30</v>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7757,31 +8061,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E149" s="6" t="n">
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" s="6" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="F149" s="6" t="n">
+      <c r="H149" s="6" t="n">
         <v>46132.70833333334</v>
       </c>
-      <c r="G149" t="n">
+      <c r="I149" t="n">
         <v>16</v>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7806,31 +8112,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E150" s="6" t="n">
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F150" s="6" t="n">
+      <c r="H150" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G150" t="n">
+      <c r="I150" t="n">
         <v>30</v>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7855,31 +8163,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E151" s="6" t="n">
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F151" s="6" t="n">
+      <c r="H151" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G151" t="n">
+      <c r="I151" t="n">
         <v>20</v>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t>GROUPE 6</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7904,31 +8214,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E152" s="6" t="n">
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" s="6" t="n">
         <v>46129.33333333334</v>
       </c>
-      <c r="F152" s="6" t="n">
+      <c r="H152" s="6" t="n">
         <v>46130.70833333334</v>
       </c>
-      <c r="G152" t="n">
+      <c r="I152" t="n">
         <v>16</v>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -7953,31 +8265,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E153" s="6" t="n">
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F153" s="6" t="n">
+      <c r="H153" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G153" t="n">
+      <c r="I153" t="n">
         <v>30</v>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8002,31 +8316,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E154" s="6" t="n">
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F154" s="6" t="n">
+      <c r="H154" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G154" t="n">
+      <c r="I154" t="n">
         <v>30</v>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8051,31 +8367,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E155" s="6" t="n">
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" s="6" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F155" s="6" t="n">
+      <c r="H155" s="6" t="n">
         <v>46178.70833333334</v>
       </c>
-      <c r="G155" t="n">
+      <c r="I155" t="n">
         <v>16</v>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8100,31 +8418,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E156" s="6" t="n">
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" s="6" t="n">
         <v>46155.33333333334</v>
       </c>
-      <c r="F156" s="6" t="n">
+      <c r="H156" s="6" t="n">
         <v>46159.70833333334</v>
       </c>
-      <c r="G156" t="n">
+      <c r="I156" t="n">
         <v>30</v>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8149,31 +8469,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E157" s="6" t="n">
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" s="6" t="n">
         <v>46175.33333333334</v>
       </c>
-      <c r="F157" s="6" t="n">
+      <c r="H157" s="6" t="n">
         <v>46176.70833333334</v>
       </c>
-      <c r="G157" t="n">
+      <c r="I157" t="n">
         <v>16</v>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8198,31 +8520,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E158" s="6" t="n">
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F158" s="6" t="n">
+      <c r="H158" s="6" t="n">
         <v>46154.70833333334</v>
       </c>
-      <c r="G158" t="n">
+      <c r="I158" t="n">
         <v>30</v>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8247,31 +8571,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E159" s="6" t="n">
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" s="6" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="F159" s="6" t="n">
+      <c r="H159" s="6" t="n">
         <v>46132.70833333334</v>
       </c>
-      <c r="G159" t="n">
+      <c r="I159" t="n">
         <v>16</v>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8296,31 +8622,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E160" s="6" t="n">
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" s="6" t="n">
         <v>46170.33333333334</v>
       </c>
-      <c r="F160" s="6" t="n">
+      <c r="H160" s="6" t="n">
         <v>46174.70833333334</v>
       </c>
-      <c r="G160" t="n">
+      <c r="I160" t="n">
         <v>30</v>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8345,31 +8673,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E161" s="6" t="n">
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" s="6" t="n">
         <v>46160.33333333334</v>
       </c>
-      <c r="F161" s="6" t="n">
+      <c r="H161" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G161" t="n">
+      <c r="I161" t="n">
         <v>20</v>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t>GROUPE 7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8394,31 +8724,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E162" s="6" t="n">
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" s="6" t="n">
         <v>46137.33333333334</v>
       </c>
-      <c r="F162" s="6" t="n">
+      <c r="H162" s="6" t="n">
         <v>46138.70833333334</v>
       </c>
-      <c r="G162" t="n">
+      <c r="I162" t="n">
         <v>16</v>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8443,31 +8775,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E163" s="6" t="n">
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" s="6" t="n">
         <v>46139.33333333334</v>
       </c>
-      <c r="F163" s="6" t="n">
+      <c r="H163" s="6" t="n">
         <v>46140.70833333334</v>
       </c>
-      <c r="G163" t="n">
+      <c r="I163" t="n">
         <v>16</v>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>FAB A</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>FAB A</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t>GROUPE 8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8492,31 +8826,33 @@
           <t>CPFAE ACG</t>
         </is>
       </c>
-      <c r="E164" s="6" t="n">
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" s="6" t="n">
         <v>46137.33333333334</v>
       </c>
-      <c r="F164" s="6" t="n">
+      <c r="H164" s="6" t="n">
         <v>46138.70833333334</v>
       </c>
-      <c r="G164" t="n">
+      <c r="I164" t="n">
         <v>16</v>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="J164" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="K164" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8541,31 +8877,33 @@
           <t>CPFAE ACG</t>
         </is>
       </c>
-      <c r="E165" s="6" t="n">
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" s="6" t="n">
         <v>46158.33333333334</v>
       </c>
-      <c r="F165" s="6" t="n">
+      <c r="H165" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G165" t="n">
+      <c r="I165" t="n">
         <v>30</v>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="J165" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="K165" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8590,31 +8928,33 @@
           <t>CPFAE ACG</t>
         </is>
       </c>
-      <c r="E166" s="6" t="n">
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F166" s="6" t="n">
+      <c r="H166" s="6" t="n">
         <v>46164.70833333334</v>
       </c>
-      <c r="G166" t="n">
+      <c r="I166" t="n">
         <v>16</v>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="J166" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="K166" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8639,31 +8979,33 @@
           <t>CPFAE ACG</t>
         </is>
       </c>
-      <c r="E167" s="6" t="n">
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" s="6" t="n">
         <v>46139.33333333334</v>
       </c>
-      <c r="F167" s="6" t="n">
+      <c r="H167" s="6" t="n">
         <v>46140.70833333334</v>
       </c>
-      <c r="G167" t="n">
+      <c r="I167" t="n">
         <v>16</v>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="J167" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8688,31 +9030,33 @@
           <t>CPFAE ACG</t>
         </is>
       </c>
-      <c r="E168" s="6" t="n">
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F168" s="6" t="n">
+      <c r="H168" s="6" t="n">
         <v>46157.70833333334</v>
       </c>
-      <c r="G168" t="n">
+      <c r="I168" t="n">
         <v>30</v>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="J168" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="K168" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8737,31 +9081,33 @@
           <t>CPFAE ACG</t>
         </is>
       </c>
-      <c r="E169" s="6" t="n">
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F169" s="6" t="n">
+      <c r="H169" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G169" t="n">
+      <c r="I169" t="n">
         <v>16</v>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="J169" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8786,31 +9132,33 @@
           <t>CPFAE ACG</t>
         </is>
       </c>
-      <c r="E170" s="6" t="n">
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F170" s="6" t="n">
+      <c r="H170" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G170" t="n">
+      <c r="I170" t="n">
         <v>30</v>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="J170" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="K170" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8835,31 +9183,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E171" s="6" t="n">
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" s="6" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="F171" s="6" t="n">
+      <c r="H171" s="6" t="n">
         <v>46138.70833333334</v>
       </c>
-      <c r="G171" t="n">
+      <c r="I171" t="n">
         <v>16</v>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="J171" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="K171" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8884,31 +9234,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E172" s="6" t="n">
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" s="6" t="n">
         <v>46158.33333333334</v>
       </c>
-      <c r="F172" s="6" t="n">
+      <c r="H172" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G172" t="n">
+      <c r="I172" t="n">
         <v>30</v>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="J172" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="K172" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8933,31 +9285,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E173" s="6" t="n">
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" s="6" t="n">
         <v>46165.33333333334</v>
       </c>
-      <c r="F173" s="6" t="n">
+      <c r="H173" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G173" t="n">
+      <c r="I173" t="n">
         <v>16</v>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="J173" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -8982,31 +9336,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E174" s="6" t="n">
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F174" s="6" t="n">
+      <c r="H174" s="6" t="n">
         <v>46164.70833333334</v>
       </c>
-      <c r="G174" t="n">
+      <c r="I174" t="n">
         <v>16</v>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="J174" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9031,31 +9387,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E175" s="6" t="n">
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F175" s="6" t="n">
+      <c r="H175" s="6" t="n">
         <v>46157.70833333334</v>
       </c>
-      <c r="G175" t="n">
+      <c r="I175" t="n">
         <v>30</v>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="J175" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="K175" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9080,31 +9438,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E176" s="6" t="n">
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F176" s="6" t="n">
+      <c r="H176" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G176" t="n">
+      <c r="I176" t="n">
         <v>16</v>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="J176" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="K176" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9129,31 +9489,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E177" s="6" t="n">
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F177" s="6" t="n">
+      <c r="H177" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G177" t="n">
+      <c r="I177" t="n">
         <v>30</v>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="J177" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="K177" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9178,31 +9540,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E178" s="6" t="n">
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" s="6" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="F178" s="6" t="n">
+      <c r="H178" s="6" t="n">
         <v>46138.70833333334</v>
       </c>
-      <c r="G178" t="n">
+      <c r="I178" t="n">
         <v>16</v>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="J178" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="K178" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9227,31 +9591,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E179" s="6" t="n">
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" s="6" t="n">
         <v>46158.33333333334</v>
       </c>
-      <c r="F179" s="6" t="n">
+      <c r="H179" s="6" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G179" t="n">
+      <c r="I179" t="n">
         <v>30</v>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="J179" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9276,31 +9642,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E180" s="6" t="n">
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" s="6" t="n">
         <v>46165.33333333334</v>
       </c>
-      <c r="F180" s="6" t="n">
+      <c r="H180" s="6" t="n">
         <v>46168.70833333334</v>
       </c>
-      <c r="G180" t="n">
+      <c r="I180" t="n">
         <v>16</v>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="J180" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9325,31 +9693,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E181" s="6" t="n">
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" s="6" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F181" s="6" t="n">
+      <c r="H181" s="6" t="n">
         <v>46164.70833333334</v>
       </c>
-      <c r="G181" t="n">
+      <c r="I181" t="n">
         <v>16</v>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="J181" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="K181" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9374,31 +9744,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E182" s="6" t="n">
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" s="6" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F182" s="6" t="n">
+      <c r="H182" s="6" t="n">
         <v>46157.70833333334</v>
       </c>
-      <c r="G182" t="n">
+      <c r="I182" t="n">
         <v>30</v>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="J182" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="K182" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9423,31 +9795,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E183" s="6" t="n">
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" s="6" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F183" s="6" t="n">
+      <c r="H183" s="6" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G183" t="n">
+      <c r="I183" t="n">
         <v>16</v>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="J183" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="K183" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -9472,31 +9846,33 @@
           <t>CPFAE AGC</t>
         </is>
       </c>
-      <c r="E184" s="6" t="n">
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" s="6" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F184" s="6" t="n">
+      <c r="H184" s="6" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G184" t="n">
+      <c r="I184" t="n">
         <v>30</v>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="J184" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="K184" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t>GROUPE 3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
